--- a/CENSOS-BOVINOS-2024-Final.xlsx
+++ b/CENSOS-BOVINOS-2024-Final.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D0EED9-F306-4F08-8DB8-EDCD39139603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOVINOS Y PREDIOS" sheetId="6" r:id="rId1"/>

--- a/CENSOS-BOVINOS-2024-Final.xlsx
+++ b/CENSOS-BOVINOS-2024-Final.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atolosa\Desktop\Python\DatosBovinos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atolosa\Downloads\AGT\Python\DatosBovinos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D0EED9-F306-4F08-8DB8-EDCD39139603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE8C2D5-4E07-4DB5-962A-40BCAA5C4865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOVINOS Y PREDIOS" sheetId="6" r:id="rId1"/>
     <sheet name="Tabla_Departamentos" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOVINOS Y PREDIOS'!$A$5:$Q$1127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOVINOS Y PREDIOS'!$A$5:$Q$1126</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tabla_Departamentos!$A$5:$O$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -7001,7 +7001,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7126,7 +7126,6 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7523,7 +7522,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:Q1134"/>
+  <dimension ref="A1:Q1133"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.85546875" customWidth="1"/>
@@ -69276,83 +69275,25 @@
       </c>
     </row>
     <row r="1127" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D1127" s="41">
-        <f t="shared" ref="D1127:P1127" si="40">SUM(D6:D1126)</f>
-        <v>3041876</v>
-      </c>
-      <c r="E1127" s="41">
-        <f t="shared" si="40"/>
-        <v>2845167</v>
-      </c>
-      <c r="F1127" s="41">
-        <f t="shared" si="40"/>
-        <v>3266134</v>
-      </c>
-      <c r="G1127" s="41">
-        <f t="shared" si="40"/>
-        <v>3240136</v>
-      </c>
-      <c r="H1127" s="41">
-        <f t="shared" si="40"/>
-        <v>3308811</v>
-      </c>
-      <c r="I1127" s="41">
-        <f t="shared" si="40"/>
-        <v>2534759</v>
-      </c>
-      <c r="J1127" s="41">
-        <f t="shared" si="40"/>
-        <v>9688955</v>
-      </c>
-      <c r="K1127" s="41">
-        <f t="shared" si="40"/>
-        <v>1277418</v>
-      </c>
-      <c r="L1127" s="41">
-        <f t="shared" si="40"/>
-        <v>29203256</v>
-      </c>
-      <c r="M1127" s="41">
-        <f t="shared" si="40"/>
-        <v>490044</v>
-      </c>
-      <c r="N1127" s="41">
-        <f t="shared" si="40"/>
-        <v>61942</v>
-      </c>
-      <c r="O1127" s="41">
-        <f t="shared" si="40"/>
-        <v>55986</v>
-      </c>
-      <c r="P1127" s="41">
-        <f t="shared" si="40"/>
-        <v>7100</v>
-      </c>
-      <c r="Q1127" s="41">
-        <f>SUM(Q6:Q1126)</f>
-        <v>615072</v>
-      </c>
+      <c r="L1127" s="9"/>
     </row>
     <row r="1128" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="L1128" s="9"/>
+      <c r="D1128" s="8"/>
+      <c r="L1128" s="8"/>
     </row>
     <row r="1129" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D1129" s="8"/>
-      <c r="L1129" s="8"/>
-    </row>
-    <row r="1130" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H1130" s="8"/>
-      <c r="M1130" s="8"/>
-      <c r="N1130" s="8"/>
-      <c r="O1130" s="8"/>
-      <c r="P1130" s="8"/>
-      <c r="Q1130" s="8"/>
-    </row>
-    <row r="1134" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="J1134" s="9"/>
+      <c r="H1129" s="8"/>
+      <c r="M1129" s="8"/>
+      <c r="N1129" s="8"/>
+      <c r="O1129" s="8"/>
+      <c r="P1129" s="8"/>
+      <c r="Q1129" s="8"/>
+    </row>
+    <row r="1133" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="J1133" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:Q1127" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A5:Q1126" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:Q1126">
     <sortCondition ref="A6:A1126"/>
     <sortCondition ref="B6:B1126"/>
@@ -69369,10 +69310,6 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="K1127:L1127 I1127:J1127 D1127:H1127" unlockedFormula="1"/>
-    <ignoredError sqref="Q173:Q181" formulaRange="1"/>
-  </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
